--- a/vulcan_rozklad_2026_2027.xlsx
+++ b/vulcan_rozklad_2026_2027.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rozkład" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +45,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,8 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -456,45 +457,10 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Podstawa programowa</t>
+          <t>Komentarz</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Komentarz</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Zasoby prywatne</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Zasoby publiczne</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Rozszerzenie</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Smartlinki</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Materiały dydaktyczne</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Kolekcja po lekcji</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Aktywna</t>
         </is>
@@ -506,7 +472,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Blok 0: Start</t>
+          <t>Co będziemy robić i po co</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -515,30 +481,15 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>III.1, III.3, IV.5</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>III.1, III.3, IV.5</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Nie</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
+          <t>0. Start</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>Tak</t>
         </is>
@@ -550,7 +501,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Blok 1: Ile internet o tobie wie?</t>
+          <t>Twoje miejsce pracy: konto, chmura, porządek w plikach</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -559,30 +510,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>IV.4, V.1, V.3, V.4, II.4</t>
+          <t>IV.5; III.1; III.3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IV.4, V.1, V.3, V.4, II.4</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Nie</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+          <t>0. Start</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>Tak</t>
         </is>
@@ -594,7 +534,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Blok 2: Napraw to zdjęcie</t>
+          <t>HACZYK: wygooglaj siebie</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -603,30 +543,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>II.3.a, II.4</t>
+          <t>IV.4; II.4</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>II.3.a, II.4</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Nie</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
+          <t>1. Ile internet o tobie wie?</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>Tak</t>
         </is>
@@ -638,7 +567,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Blok 3: Plakat, który wisi w szkole</t>
+          <t>Czy twoje hasło już wyciekło?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -647,30 +576,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>II.3.a, II.4, V.2</t>
+          <t>V.3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>II.3.a, II.4, V.2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Nie</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
+          <t>1. Ile internet o tobie wie?</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>Tak</t>
         </is>
@@ -682,7 +600,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Blok 4: Dokument, który wygląda jak z firmy</t>
+          <t>Ile trwa złamanie twojego hasła</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -691,30 +609,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>II.3.b, IV.1</t>
+          <t>V.3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>II.3.b, IV.1</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Nie</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
+          <t>1. Ile internet o tobie wie?</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Tak</t>
         </is>
@@ -726,7 +633,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Blok 5: Ile naprawdę cię to kosztuje?</t>
+          <t>Druga blokada: logowanie dwuskładnikowe</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -735,30 +642,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I.1, I.3, II.3.c, IV.1</t>
+          <t>V.3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>I.1, I.3, II.3.c, IV.1</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Nie</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
+          <t>1. Ile internet o tobie wie?</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>Tak</t>
         </is>
@@ -770,7 +666,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Blok 6: Kto to napisał — człowiek czy maszyna?</t>
+          <t>Oszustwa, które naprawdę działają</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -779,30 +675,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>II.4, III.1, IV.2, V.2</t>
+          <t>V.3; V.4; V.1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>II.4, III.1, IV.2, V.2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Nie</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
+          <t>1. Ile internet o tobie wie?</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>Tak</t>
         </is>
@@ -814,7 +699,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Blok 7: Twoja strona w internecie</t>
+          <t>FINAŁ: ściana faktów</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -823,30 +708,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>II.3.f, III.1, III.3, III.4, IV.1, IV.3</t>
+          <t>V.3; IV.4; IV.1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>II.3.f, III.1, III.3, III.4, IV.1, IV.3</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Nie</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
+          <t>1. Ile internet o tobie wie?</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>Tak</t>
         </is>
@@ -858,7 +732,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Blok 8: Zaprojektuj swoje miejsce pracy</t>
+          <t>HACZYK: czy to zdjęcie jest prawdziwe?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -867,30 +741,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I.1, II.3.a, III.2, IV.1</t>
+          <t>II.4; II.3a</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>I.1, II.3.a, III.2, IV.1</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Nie</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
+          <t>2. Napraw to zdjęcie</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>Tak</t>
         </is>
@@ -902,7 +765,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Blok 9: Dostań tę pracę</t>
+          <t>Piksel, rozdzielczość, format</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -911,30 +774,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>II.3.b, IV.1, IV.2, IV.5</t>
+          <t>II.3a</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>II.3.b, IV.1, IV.2, IV.5</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Nie</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
+          <t>2. Napraw to zdjęcie</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>Tak</t>
         </is>
@@ -946,39 +798,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Blok 10: Co mówią te dane?</t>
+          <t>Kadr, jasność, kolor</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Klasa II</t>
+          <t>Klasa I</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I.1, II.3.c, II.3.e, IV.1</t>
+          <t>II.3a</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>I.1, II.3.c, II.3.e, IV.1</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Nie</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
+          <t>2. Napraw to zdjęcie</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>Tak</t>
         </is>
@@ -990,39 +831,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Blok 11: Gdzie właściwie są te dane?</t>
+          <t>Usuń to ze zdjęcia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Klasa II</t>
+          <t>Klasa I</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>II.3.d, IV.1, V.1</t>
+          <t>II.3a</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>II.3.d, IV.1, V.1</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Nie</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
+          <t>2. Napraw to zdjęcie</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>Tak</t>
         </is>
@@ -1034,39 +864,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Blok 12: Każ komputerowi zrobić to za ciebie</t>
+          <t>FINAŁ: zgadywanka przed i po</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Klasa II</t>
+          <t>Klasa I</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I.1, I.2.a, I.2.b, I.2.c, I.2.d, I.3, II.1, II.2, IV.1, V.3</t>
+          <t>II.3a; IV.1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>I.1, I.2.a, I.2.b, I.2.c, I.2.d, I.3, II.1, II.2, IV.1, V.3</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Nie</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
+          <t>2. Napraw to zdjęcie</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>Tak</t>
         </is>
@@ -1078,39 +897,2536 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Blok 13: Co potrafisz?</t>
+          <t>HACZYK: dlaczego jeden plakat działa, a drugi nie</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>II.4</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>3. Plakat, który wisi w szkole</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Wektor kontra raster</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>II.3a</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>3. Plakat, który wisi w szkole</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Skąd wziąć grafikę legalnie</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>V.2</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>3. Plakat, który wisi w szkole</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kolory, czcionki, kompozycja</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>II.3a</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>3. Plakat, który wisi w szkole</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Przygotowanie do druku</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>II.3a</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>3. Plakat, który wisi w szkole</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>FINAŁ: wernisaż na korytarzu</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>II.3a; IV.1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>3. Plakat, który wisi w szkole</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HACZYK: 5 grzechów, po których widać amatora</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>II.3b</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>4. Dokument, który wygląda jak z firmy</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Style — jeden klik zmienia cały dokument</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>II.3b</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>4. Dokument, który wygląda jak z firmy</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sekcje, kolumny, numeracja stron</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>II.3b</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>4. Dokument, który wygląda jak z firmy</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tabela, którą da się czytać</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>II.3b</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>4. Dokument, który wygląda jak z firmy</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Spis treści, który sam się aktualizuje</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>II.3b</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>4. Dokument, który wygląda jak z firmy</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Recenzja: poprawiam cudzy dokument</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>II.3b; IV.1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>4. Dokument, który wygląda jak z firmy</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Jeden szablon, dwadzieścia pism</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>II.3b</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>4. Dokument, który wygląda jak z firmy</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FINAŁ: poczta klasowa</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>II.3b; IV.1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>4. Dokument, który wygląda jak z firmy</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>HACZYK: policz to na kartce</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>I.1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>5. Ile naprawdę cię to kosztuje?</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Arkusz: komórka, adres, pierwsza formuła</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>II.3c</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>5. Ile naprawdę cię to kosztuje?</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Jedna zmiana, cały arkusz się przelicza</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>II.3c</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>5. Ile naprawdę cię to kosztuje?</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SUMA, ŚREDNIA, MIN, MAX</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>II.3c</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>5. Ile naprawdę cię to kosztuje?</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>JEŻELI + formatowanie warunkowe: arkusz sam ostrzega</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>II.3c</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>5. Ile naprawdę cię to kosztuje?</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Kalkulator zawodowy</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>II.3c; I.1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>5. Ile naprawdę cię to kosztuje?</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sprawdzian praktyczny — arkusz</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>II.3c</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>5. Ile naprawdę cię to kosztuje?</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FINAŁ: liczba, która zaskakuje</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>II.3c; I.3; IV.1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>5. Ile naprawdę cię to kosztuje?</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>HACZYK: turniej „człowiek czy AI”</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>II.4</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>6. Kto to napisał — człowiek czy maszyna?</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Co to właściwie jest i skąd bierze odpowiedzi</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>II.4; III.1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>6. Kto to napisał — człowiek czy maszyna?</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Polowanie na kłamstwa</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>II.4</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>6. Kto to napisał — człowiek czy maszyna?</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Jak pytać, żeby dostać coś sensownego</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>II.4; V.2</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>6. Kto to napisał — człowiek czy maszyna?</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>FINAŁ: pułapka na AI</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>II.4; V.2; IV.2</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>6. Kto to napisał — człowiek czy maszyna?</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>HACZYK: co się dzieje, gdy wpisujesz adres</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>III.4; III.1; III.3</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>7. Twoja strona w internecie</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Pierwszy plik HTML</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>II.3f</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>7. Twoja strona w internecie</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Struktura: nagłówki i sekcje</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>II.3f</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>7. Twoja strona w internecie</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Obrazy, listy i odnośniki</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>II.3f</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>7. Twoja strona w internecie</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Tabela na stronie</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>II.3f</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>7. Twoja strona w internecie</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CSS: jeden plik zmienia wszystko</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>II.3f</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>7. Twoja strona w internecie</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Układ, przyciski, sekcja kontakt</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>II.3f</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>7. Twoja strona w internecie</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Czy każdy z niej skorzysta?</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>IV.3; II.3f</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>7. Twoja strona w internecie</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>FINAŁ: to jest w internecie</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>II.3f; IV.1</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>7. Twoja strona w internecie</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>HACZYK: rozplanuj to na kartce</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>II.3a; I.1</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>8. Zaprojektuj swoje miejsce pracy</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Od płaskiego do przestrzennego</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>II.3a</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>8. Zaprojektuj swoje miejsce pracy</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Sweet Home 3D: ściany i wymiary</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>II.3a</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>8. Zaprojektuj swoje miejsce pracy</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Kolory, materiały, widok z wnętrza</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>II.3a</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>8. Zaprojektuj swoje miejsce pracy</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Wyposażenie stanowiska</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>II.3a; III.2</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>8. Zaprojektuj swoje miejsce pracy</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FINAŁ: spacer po projektach</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>II.3a; III.2; IV.1</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>8. Zaprojektuj swoje miejsce pracy</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>HACZYK: 7 sekund na CV</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>II.3b; IV.2</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>9. Dostań tę pracę</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Twoje CV</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>II.3b</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>9. Dostań tę pracę</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Wiadomość do pracodawcy</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>II.3b; IV.2</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>9. Dostań tę pracę</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Sprawy, które załatwisz sam</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>IV.2</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>9. Dostań tę pracę</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>FINAŁ: rekrutacja na niby</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Klasa I</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>II.3b; IV.1; IV.5</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>9. Dostań tę pracę</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>HACZYK: twoja klasa w liczbach</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
           <t>Klasa II</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>II.3.e, II.4, IV.1, IV.2, IV.5, V.2</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>II.3.e, II.4, IV.1, IV.2, IV.5, V.2</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Nie</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>I.1; II.3c</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>10. Co mówią te dane?</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Porządkowanie: sortowanie i filtry</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>II.3c</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>10. Co mówią te dane?</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>LICZ.JEŻELI i SUMA.JEŻELI</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>II.3c</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>10. Co mówią te dane?</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Arkusz sam znajduje dane</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>II.3c</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>10. Co mówią te dane?</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Tabela przestawna</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>II.3c</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>10. Co mówią te dane?</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Wykresy przestawne i fragmentatory</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>II.3c</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>10. Co mówią te dane?</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Sprawdzian praktyczny — analiza danych</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>II.3c</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>10. Co mówią te dane?</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>FINAŁ: narada zarządu — 3 liczby, 2 wykresy, 1 rekomendacja</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>II.3c; IV.1; II.3e</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>10. Co mówią te dane?</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>HACZYK: znajdź to w arkuszu</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>II.3d</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>11. Gdzie właściwie są te dane?</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Tabela, rekord, klucz</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>II.3d</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>11. Gdzie właściwie są te dane?</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Dwie tabele i relacja</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>II.3d</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>11. Gdzie właściwie są te dane?</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Kwerendy: baza odpowiada na pytania</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>II.3d</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>11. Gdzie właściwie są te dane?</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Formularz i RODO</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>II.3d; V.1</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>11. Gdzie właściwie są te dane?</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>FINAŁ: test na żywo</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>II.3d; IV.1</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>11. Gdzie właściwie są te dane?</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>HACZYK: instrukcja dla kogoś, kto nie myśli</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>I.1</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>12. Każ komputerowi zrobić to za ciebie</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Pierwszy program</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>II.1</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>12. Każ komputerowi zrobić to za ciebie</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Program podejmuje decyzję</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>II.1</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>12. Każ komputerowi zrobić to za ciebie</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Powtarzanie: pętla</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>II.1</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>12. Każ komputerowi zrobić to za ciebie</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Lista i statystyki</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>II.1; I.2d</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>12. Każ komputerowi zrobić to za ciebie</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Własna funkcja; czym to zrobić</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>II.1; II.2</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>12. Każ komputerowi zrobić to za ciebie</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>NWD: skracanie proporcji mieszanki</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>I.2a</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>12. Każ komputerowi zrobić to za ciebie</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Jak komputer zapisuje liczby</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>I.2a</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>12. Każ komputerowi zrobić to za ciebie</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Sortowanie i szukanie wzorca</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>I.2b; I.2c</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>12. Każ komputerowi zrobić to za ciebie</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Ciąg Fibonacciego i złota proporcja</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>I.2e</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>12. Każ komputerowi zrobić to za ciebie</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Szyfr, który złamiesz</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>I.2b; V.3</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>12. Każ komputerowi zrobić to za ciebie</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Znajdź błąd</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>I.3; II.1</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>12. Każ komputerowi zrobić to za ciebie</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>FINAŁ: to działa</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>II.1; IV.1</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>12. Każ komputerowi zrobić to za ciebie</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>AI w twoim zawodzie — na co uważać</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>II.4; V.2; IV.2</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>13. Co potrafisz?</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Portfolio: zbierz to wszystko</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>IV.5; II.3e</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>13. Co potrafisz?</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>FINAŁ: 3 minuty o tym, co umiesz</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Klasa II</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>IV.1; II.3e</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>13. Co potrafisz?</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
         <is>
           <t>Tak</t>
         </is>
